--- a/SCE_skewness.xlsx
+++ b/SCE_skewness.xlsx
@@ -75,7 +75,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -148,13 +148,13 @@
         <v>0.75467979907989502</v>
       </c>
       <c r="C7" s="2">
-        <v>0.37337955832481384</v>
+        <v>0.38950255513191223</v>
       </c>
       <c r="D7" s="2">
         <v>0.30358356237411499</v>
       </c>
       <c r="E7" s="2">
-        <v>0.02568526566028595</v>
+        <v>0.035367846488952637</v>
       </c>
     </row>
     <row r="8">
@@ -165,13 +165,13 @@
         <v>0.45104503631591797</v>
       </c>
       <c r="C8" s="2">
-        <v>0.18892766535282135</v>
+        <v>0.20146670937538147</v>
       </c>
       <c r="D8" s="2">
         <v>0.10388252884149551</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.16413420438766479</v>
+        <v>-0.15381449460983276</v>
       </c>
     </row>
     <row r="9">
@@ -182,13 +182,13 @@
         <v>0.52031427621841431</v>
       </c>
       <c r="C9" s="2">
-        <v>0.2265809178352356</v>
+        <v>0.23372864723205566</v>
       </c>
       <c r="D9" s="2">
         <v>0.10086610168218613</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.18826974928379059</v>
+        <v>-0.17784759402275085</v>
       </c>
     </row>
     <row r="10">
@@ -199,13 +199,13 @@
         <v>-0.22879557311534882</v>
       </c>
       <c r="C10" s="2">
-        <v>-0.30928468704223633</v>
+        <v>-0.30443152785301208</v>
       </c>
       <c r="D10" s="2">
         <v>0.15720002353191376</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.13564604520797729</v>
+        <v>-0.12567031383514404</v>
       </c>
     </row>
     <row r="11">
@@ -216,13 +216,13 @@
         <v>0.020674310624599457</v>
       </c>
       <c r="C11" s="2">
-        <v>-0.35117712616920471</v>
+        <v>-0.3434271514415741</v>
       </c>
       <c r="D11" s="2">
         <v>0.11538553237915039</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.19134916365146637</v>
+        <v>-0.18098142743110657</v>
       </c>
     </row>
     <row r="12">
@@ -233,13 +233,13 @@
         <v>-0.89462268352508545</v>
       </c>
       <c r="C12" s="2">
-        <v>-1.1132315397262573</v>
+        <v>-1.0997262001037598</v>
       </c>
       <c r="D12" s="2">
         <v>0.030098624527454376</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.26107761263847351</v>
+        <v>-0.25189825892448425</v>
       </c>
     </row>
     <row r="13">
@@ -250,13 +250,13 @@
         <v>0.082767561078071594</v>
       </c>
       <c r="C13" s="2">
-        <v>-0.33308303356170654</v>
+        <v>-0.3220461905002594</v>
       </c>
       <c r="D13" s="2">
         <v>-0.13790342211723328</v>
       </c>
       <c r="E13" s="2">
-        <v>-0.44181504845619202</v>
+        <v>-0.43418183922767639</v>
       </c>
     </row>
     <row r="14">
@@ -267,13 +267,13 @@
         <v>0.55153751373291016</v>
       </c>
       <c r="C14" s="2">
-        <v>0.23271985352039337</v>
+        <v>0.23957066237926483</v>
       </c>
       <c r="D14" s="2">
         <v>-0.136473149061203</v>
       </c>
       <c r="E14" s="2">
-        <v>-0.43374499678611755</v>
+        <v>-0.42622286081314087</v>
       </c>
     </row>
     <row r="15">
@@ -284,13 +284,13 @@
         <v>-0.21913042664527893</v>
       </c>
       <c r="C15" s="2">
-        <v>-0.636974036693573</v>
+        <v>-0.62347036600112915</v>
       </c>
       <c r="D15" s="2">
         <v>-0.18043906986713409</v>
       </c>
       <c r="E15" s="2">
-        <v>-0.51276034116744995</v>
+        <v>-0.50568932294845581</v>
       </c>
     </row>
     <row r="16">
@@ -301,13 +301,13 @@
         <v>-0.012902386486530304</v>
       </c>
       <c r="C16" s="2">
-        <v>-0.25417646765708923</v>
+        <v>-0.24874891340732574</v>
       </c>
       <c r="D16" s="2">
         <v>-0.19662326574325562</v>
       </c>
       <c r="E16" s="2">
-        <v>-0.51716363430023193</v>
+        <v>-0.51111936569213867</v>
       </c>
     </row>
     <row r="17">
@@ -318,13 +318,13 @@
         <v>-1.0609734058380127</v>
       </c>
       <c r="C17" s="2">
-        <v>-1.4377092123031616</v>
+        <v>-1.4390854835510254</v>
       </c>
       <c r="D17" s="2">
         <v>-0.14019788801670074</v>
       </c>
       <c r="E17" s="2">
-        <v>-0.49307277798652649</v>
+        <v>-0.48668131232261658</v>
       </c>
     </row>
     <row r="18">
@@ -335,13 +335,13 @@
         <v>0.53318673372268677</v>
       </c>
       <c r="C18" s="2">
-        <v>0.29921138286590576</v>
+        <v>0.30535939335823059</v>
       </c>
       <c r="D18" s="2">
         <v>-0.16055162250995636</v>
       </c>
       <c r="E18" s="2">
-        <v>-0.49475118517875671</v>
+        <v>-0.48858961462974548</v>
       </c>
     </row>
     <row r="19">
@@ -352,13 +352,13 @@
         <v>-0.62448883056640625</v>
       </c>
       <c r="C19" s="2">
-        <v>-1.0204226970672607</v>
+        <v>-1.0196297168731689</v>
       </c>
       <c r="D19" s="2">
         <v>-0.25215312838554382</v>
       </c>
       <c r="E19" s="2">
-        <v>-0.59468656778335571</v>
+        <v>-0.58793234825134277</v>
       </c>
     </row>
     <row r="20">
@@ -369,13 +369,13 @@
         <v>-0.12498348951339722</v>
       </c>
       <c r="C20" s="2">
-        <v>-0.39080685377120972</v>
+        <v>-0.39229744672775269</v>
       </c>
       <c r="D20" s="2">
         <v>-0.22514151036739349</v>
       </c>
       <c r="E20" s="2">
-        <v>-0.5390288233757019</v>
+        <v>-0.53289985656738281</v>
       </c>
     </row>
     <row r="21">
@@ -386,13 +386,13 @@
         <v>-0.38679426908493042</v>
       </c>
       <c r="C21" s="2">
-        <v>-0.89641386270523071</v>
+        <v>-0.8797837495803833</v>
       </c>
       <c r="D21" s="2">
         <v>-0.27614706754684448</v>
       </c>
       <c r="E21" s="2">
-        <v>-0.59278202056884766</v>
+        <v>-0.58642667531967163</v>
       </c>
     </row>
     <row r="22">
@@ -403,13 +403,13 @@
         <v>-0.10041602700948715</v>
       </c>
       <c r="C22" s="2">
-        <v>-0.34818866848945618</v>
+        <v>-0.33922085165977478</v>
       </c>
       <c r="D22" s="2">
         <v>-0.2092270702123642</v>
       </c>
       <c r="E22" s="2">
-        <v>-0.50142329931259155</v>
+        <v>-0.49541264772415161</v>
       </c>
     </row>
     <row r="23">
@@ -420,13 +420,13 @@
         <v>-0.27287611365318298</v>
       </c>
       <c r="C23" s="2">
-        <v>-0.66669869422912598</v>
+        <v>-0.65451425313949585</v>
       </c>
       <c r="D23" s="2">
         <v>-0.29087939858436584</v>
       </c>
       <c r="E23" s="2">
-        <v>-0.58444178104400635</v>
+        <v>-0.57784497737884521</v>
       </c>
     </row>
     <row r="24">
@@ -437,13 +437,13 @@
         <v>0.023974135518074036</v>
       </c>
       <c r="C24" s="2">
-        <v>-0.13605433702468872</v>
+        <v>-0.1281777024269104</v>
       </c>
       <c r="D24" s="2">
         <v>-0.24808692932128906</v>
       </c>
       <c r="E24" s="2">
-        <v>-0.53903239965438843</v>
+        <v>-0.53130340576171875</v>
       </c>
     </row>
     <row r="25">
@@ -454,13 +454,13 @@
         <v>-0.4719524085521698</v>
       </c>
       <c r="C25" s="2">
-        <v>-0.73795551061630249</v>
+        <v>-0.73049008846282959</v>
       </c>
       <c r="D25" s="2">
         <v>-0.31977397203445435</v>
       </c>
       <c r="E25" s="2">
-        <v>-0.61176478862762451</v>
+        <v>-0.60357129573822021</v>
       </c>
     </row>
     <row r="26">
@@ -471,13 +471,13 @@
         <v>-0.45869335532188416</v>
       </c>
       <c r="C26" s="2">
-        <v>-0.61548060178756714</v>
+        <v>-0.61995947360992432</v>
       </c>
       <c r="D26" s="2">
         <v>-0.21627253293991089</v>
       </c>
       <c r="E26" s="2">
-        <v>-0.47655096650123596</v>
+        <v>-0.4689599871635437</v>
       </c>
     </row>
     <row r="27">
@@ -488,13 +488,13 @@
         <v>-0.2016841322183609</v>
       </c>
       <c r="C27" s="2">
-        <v>-0.44795498251914978</v>
+        <v>-0.436531662940979</v>
       </c>
       <c r="D27" s="2">
         <v>-0.15139244496822357</v>
       </c>
       <c r="E27" s="2">
-        <v>-0.40867984294891357</v>
+        <v>-0.40245994925498962</v>
       </c>
     </row>
     <row r="28">
@@ -505,13 +505,13 @@
         <v>-0.23935668170452118</v>
       </c>
       <c r="C28" s="2">
-        <v>-0.61173796653747559</v>
+        <v>-0.60075569152832031</v>
       </c>
       <c r="D28" s="2">
         <v>-0.093287214636802673</v>
       </c>
       <c r="E28" s="2">
-        <v>-0.33605358004570007</v>
+        <v>-0.33121782541275024</v>
       </c>
     </row>
     <row r="29">
@@ -522,13 +522,13 @@
         <v>-0.77016687393188477</v>
       </c>
       <c r="C29" s="2">
-        <v>-1.0453985929489136</v>
+        <v>-1.0427079200744629</v>
       </c>
       <c r="D29" s="2">
         <v>-0.1603572815656662</v>
       </c>
       <c r="E29" s="2">
-        <v>-0.40825349092483521</v>
+        <v>-0.40347194671630859</v>
       </c>
     </row>
     <row r="30">
@@ -539,13 +539,13 @@
         <v>0.54471868276596069</v>
       </c>
       <c r="C30" s="2">
-        <v>0.32051053643226624</v>
+        <v>0.33171769976615906</v>
       </c>
       <c r="D30" s="2">
         <v>-0.097807548940181732</v>
       </c>
       <c r="E30" s="2">
-        <v>-0.3416256308555603</v>
+        <v>-0.33593267202377319</v>
       </c>
     </row>
     <row r="31">
@@ -556,13 +556,13 @@
         <v>0.48350468277931213</v>
       </c>
       <c r="C31" s="2">
-        <v>0.26265150308609009</v>
+        <v>0.25927960872650146</v>
       </c>
       <c r="D31" s="2">
         <v>-0.10886616259813309</v>
       </c>
       <c r="E31" s="2">
-        <v>-0.37845537066459656</v>
+        <v>-0.37105491757392883</v>
       </c>
     </row>
     <row r="32">
@@ -573,13 +573,13 @@
         <v>0.25007104873657227</v>
       </c>
       <c r="C32" s="2">
-        <v>-0.013062305748462677</v>
+        <v>-0.013335241936147213</v>
       </c>
       <c r="D32" s="2">
         <v>-0.21468514204025269</v>
       </c>
       <c r="E32" s="2">
-        <v>-0.50190573930740356</v>
+        <v>-0.49483424425125122</v>
       </c>
     </row>
     <row r="33">
@@ -590,13 +590,13 @@
         <v>-0.57965648174285889</v>
       </c>
       <c r="C33" s="2">
-        <v>-0.78585362434387207</v>
+        <v>-0.77846473455429077</v>
       </c>
       <c r="D33" s="2">
         <v>-0.1857101172208786</v>
       </c>
       <c r="E33" s="2">
-        <v>-0.46395048499107361</v>
+        <v>-0.45518335700035095</v>
       </c>
     </row>
     <row r="34">
@@ -607,13 +607,13 @@
         <v>0.090995185077190399</v>
       </c>
       <c r="C34" s="2">
-        <v>-0.13830468058586121</v>
+        <v>-0.12263655662536621</v>
       </c>
       <c r="D34" s="2">
         <v>-0.086152300238609314</v>
       </c>
       <c r="E34" s="2">
-        <v>-0.35510843992233276</v>
+        <v>-0.3472042977809906</v>
       </c>
     </row>
     <row r="35">
@@ -624,13 +624,13 @@
         <v>-0.55822086334228516</v>
       </c>
       <c r="C35" s="2">
-        <v>-0.94694817066192627</v>
+        <v>-0.93605989217758179</v>
       </c>
       <c r="D35" s="2">
         <v>-0.11454352736473083</v>
       </c>
       <c r="E35" s="2">
-        <v>-0.38788989186286926</v>
+        <v>-0.38191592693328857</v>
       </c>
     </row>
     <row r="36">
@@ -641,13 +641,13 @@
         <v>-1.1540549993515015</v>
       </c>
       <c r="C36" s="2">
-        <v>-1.5590084791183472</v>
+        <v>-1.5505454540252686</v>
       </c>
       <c r="D36" s="2">
         <v>-0.17915503680706024</v>
       </c>
       <c r="E36" s="2">
-        <v>-0.44776847958564758</v>
+        <v>-0.44221380352973938</v>
       </c>
     </row>
     <row r="37">
@@ -658,13 +658,13 @@
         <v>0.021418565884232521</v>
       </c>
       <c r="C37" s="2">
-        <v>-0.27014046907424927</v>
+        <v>-0.2438977062702179</v>
       </c>
       <c r="D37" s="2">
         <v>-0.1833871603012085</v>
       </c>
       <c r="E37" s="2">
-        <v>-0.45036318898200989</v>
+        <v>-0.44530150294303894</v>
       </c>
     </row>
     <row r="38">
@@ -675,13 +675,13 @@
         <v>0.12585350871086121</v>
       </c>
       <c r="C38" s="2">
-        <v>-0.065820306539535522</v>
+        <v>-0.07089640200138092</v>
       </c>
       <c r="D38" s="2">
         <v>-0.19518217444419861</v>
       </c>
       <c r="E38" s="2">
-        <v>-0.50150567293167114</v>
+        <v>-0.49662795662879944</v>
       </c>
     </row>
     <row r="39">
@@ -692,13 +692,13 @@
         <v>0.28919762372970581</v>
       </c>
       <c r="C39" s="2">
-        <v>0.025477409362792969</v>
+        <v>0.01931309886276722</v>
       </c>
       <c r="D39" s="2">
         <v>-0.15041124820709229</v>
       </c>
       <c r="E39" s="2">
-        <v>-0.42923125624656677</v>
+        <v>-0.42507347464561462</v>
       </c>
     </row>
     <row r="40">
@@ -709,13 +709,13 @@
         <v>-0.097998887300491333</v>
       </c>
       <c r="C40" s="2">
-        <v>-0.27625578641891479</v>
+        <v>-0.28340122103691101</v>
       </c>
       <c r="D40" s="2">
         <v>-0.075663968920707703</v>
       </c>
       <c r="E40" s="2">
-        <v>-0.365407794713974</v>
+        <v>-0.36061131954193115</v>
       </c>
     </row>
     <row r="41">
@@ -726,13 +726,13 @@
         <v>0.21198192238807678</v>
       </c>
       <c r="C41" s="2">
-        <v>-0.036414600908756256</v>
+        <v>-0.041124790906906128</v>
       </c>
       <c r="D41" s="2">
         <v>0.0076738409698009491</v>
       </c>
       <c r="E41" s="2">
-        <v>-0.26977312564849854</v>
+        <v>-0.26471209526062012</v>
       </c>
     </row>
     <row r="42">
@@ -743,13 +743,13 @@
         <v>-0.68581163883209229</v>
       </c>
       <c r="C42" s="2">
-        <v>-1.2461357116699219</v>
+        <v>-1.2404026985168457</v>
       </c>
       <c r="D42" s="2">
         <v>0.037948276847600937</v>
       </c>
       <c r="E42" s="2">
-        <v>-0.24209095537662506</v>
+        <v>-0.23966348171234131</v>
       </c>
     </row>
     <row r="43">
@@ -760,13 +760,13 @@
         <v>0.49393346905708313</v>
       </c>
       <c r="C43" s="2">
-        <v>0.51216477155685425</v>
+        <v>0.52135384082794189</v>
       </c>
       <c r="D43" s="2">
         <v>0.027599811553955078</v>
       </c>
       <c r="E43" s="2">
-        <v>-0.27720198035240173</v>
+        <v>-0.27242377400398254</v>
       </c>
     </row>
     <row r="44">
@@ -777,13 +777,13 @@
         <v>0.11450470983982086</v>
       </c>
       <c r="C44" s="2">
-        <v>-0.37253689765930176</v>
+        <v>-0.35590055584907532</v>
       </c>
       <c r="D44" s="2">
         <v>-0.048547346144914627</v>
       </c>
       <c r="E44" s="2">
-        <v>-0.32933053374290466</v>
+        <v>-0.32457178831100464</v>
       </c>
     </row>
     <row r="45">
@@ -794,13 +794,13 @@
         <v>-0.4040147066116333</v>
       </c>
       <c r="C45" s="2">
-        <v>-0.69829648733139038</v>
+        <v>-0.68745243549346924</v>
       </c>
       <c r="D45" s="2">
         <v>-0.081148959696292877</v>
       </c>
       <c r="E45" s="2">
-        <v>-0.37052679061889648</v>
+        <v>-0.3657815158367157</v>
       </c>
     </row>
     <row r="46">
@@ -811,13 +811,13 @@
         <v>0.29388847947120667</v>
       </c>
       <c r="C46" s="2">
-        <v>-0.021000979468226433</v>
+        <v>-0.018460189923644066</v>
       </c>
       <c r="D46" s="2">
         <v>-0.1598929762840271</v>
       </c>
       <c r="E46" s="2">
-        <v>-0.44842860102653503</v>
+        <v>-0.44285738468170166</v>
       </c>
     </row>
     <row r="47">
@@ -828,13 +828,13 @@
         <v>0.032717324793338776</v>
       </c>
       <c r="C47" s="2">
-        <v>-0.38181942701339722</v>
+        <v>-0.36573910713195801</v>
       </c>
       <c r="D47" s="2">
         <v>-0.14775112271308899</v>
       </c>
       <c r="E47" s="2">
-        <v>-0.40203151106834412</v>
+        <v>-0.39691761136054993</v>
       </c>
     </row>
     <row r="48">
@@ -845,13 +845,13 @@
         <v>-0.39612677693367004</v>
       </c>
       <c r="C48" s="2">
-        <v>-0.44367972016334534</v>
+        <v>-0.45001891255378723</v>
       </c>
       <c r="D48" s="2">
         <v>-0.27623826265335083</v>
       </c>
       <c r="E48" s="2">
-        <v>-0.56342154741287231</v>
+        <v>-0.55897456407546997</v>
       </c>
     </row>
     <row r="49">
@@ -862,13 +862,13 @@
         <v>-0.39141345024108887</v>
       </c>
       <c r="C49" s="2">
-        <v>-0.64702218770980835</v>
+        <v>-0.65428882837295532</v>
       </c>
       <c r="D49" s="2">
         <v>-0.27205902338027954</v>
       </c>
       <c r="E49" s="2">
-        <v>-0.53750693798065186</v>
+        <v>-0.53377389907836914</v>
       </c>
     </row>
     <row r="50">
@@ -879,13 +879,13 @@
         <v>-0.49671423435211182</v>
       </c>
       <c r="C50" s="2">
-        <v>-0.73753088712692261</v>
+        <v>-0.73480767011642456</v>
       </c>
       <c r="D50" s="2">
         <v>-0.25660091638565063</v>
       </c>
       <c r="E50" s="2">
-        <v>-0.51418614387512207</v>
+        <v>-0.51189213991165161</v>
       </c>
     </row>
     <row r="51">
@@ -896,13 +896,13 @@
         <v>-0.57653486728668213</v>
       </c>
       <c r="C51" s="2">
-        <v>-0.82856184244155884</v>
+        <v>-0.82694464921951294</v>
       </c>
       <c r="D51" s="2">
         <v>-0.32184427976608276</v>
       </c>
       <c r="E51" s="2">
-        <v>-0.57549870014190674</v>
+        <v>-0.57235771417617798</v>
       </c>
     </row>
     <row r="52">
@@ -913,13 +913,13 @@
         <v>-0.66245073080062866</v>
       </c>
       <c r="C52" s="2">
-        <v>-0.94034546613693237</v>
+        <v>-0.93715846538543701</v>
       </c>
       <c r="D52" s="2">
         <v>-0.33927956223487854</v>
       </c>
       <c r="E52" s="2">
-        <v>-0.56610667705535889</v>
+        <v>-0.5647856593132019</v>
       </c>
     </row>
     <row r="53">
@@ -930,13 +930,13 @@
         <v>0.15211783349514008</v>
       </c>
       <c r="C53" s="2">
-        <v>-0.13930535316467285</v>
+        <v>-0.12909471988677979</v>
       </c>
       <c r="D53" s="2">
         <v>-0.35259756445884705</v>
       </c>
       <c r="E53" s="2">
-        <v>-0.61612677574157715</v>
+        <v>-0.61265301704406738</v>
       </c>
     </row>
     <row r="54">
@@ -947,13 +947,13 @@
         <v>-0.26489183306694031</v>
       </c>
       <c r="C54" s="2">
-        <v>-0.48840954899787903</v>
+        <v>-0.49051696062088013</v>
       </c>
       <c r="D54" s="2">
         <v>-0.30641192197799683</v>
       </c>
       <c r="E54" s="2">
-        <v>-0.57676118612289429</v>
+        <v>-0.57146275043487549</v>
       </c>
     </row>
     <row r="55">
@@ -964,13 +964,13 @@
         <v>-0.29330176115036011</v>
       </c>
       <c r="C55" s="2">
-        <v>-0.57281386852264404</v>
+        <v>-0.56265002489089966</v>
       </c>
       <c r="D55" s="2">
         <v>-0.32997885346412659</v>
       </c>
       <c r="E55" s="2">
-        <v>-0.60386437177658081</v>
+        <v>-0.59784907102584839</v>
       </c>
     </row>
     <row r="56">
@@ -981,13 +981,13 @@
         <v>-0.12420023232698441</v>
       </c>
       <c r="C56" s="2">
-        <v>-0.29729107022285461</v>
+        <v>-0.29759079217910767</v>
       </c>
       <c r="D56" s="2">
         <v>-0.35911431908607483</v>
       </c>
       <c r="E56" s="2">
-        <v>-0.64386242628097534</v>
+        <v>-0.6379859447479248</v>
       </c>
     </row>
     <row r="57">
@@ -998,13 +998,13 @@
         <v>-0.51598882675170898</v>
       </c>
       <c r="C57" s="2">
-        <v>-0.89386099576950073</v>
+        <v>-0.88082516193389893</v>
       </c>
       <c r="D57" s="2">
         <v>-0.24196623265743256</v>
       </c>
       <c r="E57" s="2">
-        <v>-0.53505933284759521</v>
+        <v>-0.52791255712509155</v>
       </c>
     </row>
     <row r="58">
@@ -1015,13 +1015,13 @@
         <v>0.024257250130176544</v>
       </c>
       <c r="C58" s="2">
-        <v>-0.29273155331611633</v>
+        <v>-0.28357633948326111</v>
       </c>
       <c r="D58" s="2">
         <v>-0.30076441168785095</v>
       </c>
       <c r="E58" s="2">
-        <v>-0.60341405868530273</v>
+        <v>-0.59576767683029175</v>
       </c>
     </row>
     <row r="59">
@@ -1032,13 +1032,13 @@
         <v>-0.7088165283203125</v>
       </c>
       <c r="C59" s="2">
-        <v>-0.98145973682403564</v>
+        <v>-0.97228437662124634</v>
       </c>
       <c r="D59" s="2">
         <v>-0.29284968972206116</v>
       </c>
       <c r="E59" s="2">
-        <v>-0.60051560401916504</v>
+        <v>-0.59278202056884766</v>
       </c>
     </row>
     <row r="60">
@@ -1049,13 +1049,13 @@
         <v>-0.83875411748886108</v>
       </c>
       <c r="C60" s="2">
-        <v>-1.1885443925857544</v>
+        <v>-1.1881766319274902</v>
       </c>
       <c r="D60" s="2">
         <v>-0.31478077173233032</v>
       </c>
       <c r="E60" s="2">
-        <v>-0.64107418060302734</v>
+        <v>-0.63373655080795288</v>
       </c>
     </row>
     <row r="61">
@@ -1066,13 +1066,13 @@
         <v>0.39188209176063538</v>
       </c>
       <c r="C61" s="2">
-        <v>0.038882255554199219</v>
+        <v>0.05350210890173912</v>
       </c>
       <c r="D61" s="2">
         <v>-0.32838353514671326</v>
       </c>
       <c r="E61" s="2">
-        <v>-0.67621862888336182</v>
+        <v>-0.66814017295837402</v>
       </c>
     </row>
     <row r="62">
@@ -1083,13 +1083,13 @@
         <v>-0.37706586718559265</v>
       </c>
       <c r="C62" s="2">
-        <v>-0.75449752807617188</v>
+        <v>-0.73979079723358154</v>
       </c>
       <c r="D62" s="2">
         <v>-0.32985919713973999</v>
       </c>
       <c r="E62" s="2">
-        <v>-0.66980671882629395</v>
+        <v>-0.66312772035598755</v>
       </c>
     </row>
     <row r="63">
@@ -1100,13 +1100,13 @@
         <v>-0.19365914165973663</v>
       </c>
       <c r="C63" s="2">
-        <v>-0.462323397397995</v>
+        <v>-0.46364599466323853</v>
       </c>
       <c r="D63" s="2">
         <v>-0.24417248368263245</v>
       </c>
       <c r="E63" s="2">
-        <v>-0.5722273588180542</v>
+        <v>-0.56525087356567383</v>
       </c>
     </row>
     <row r="64">
@@ -1117,13 +1117,13 @@
         <v>-0.49068161845207214</v>
       </c>
       <c r="C64" s="2">
-        <v>-0.93784123659133911</v>
+        <v>-0.93124115467071533</v>
       </c>
       <c r="D64" s="2">
         <v>-0.21772113442420959</v>
       </c>
       <c r="E64" s="2">
-        <v>-0.55255210399627686</v>
+        <v>-0.54427915811538696</v>
       </c>
     </row>
     <row r="65">
@@ -1134,13 +1134,13 @@
         <v>-0.24662499129772186</v>
       </c>
       <c r="C65" s="2">
-        <v>-0.61359125375747681</v>
+        <v>-0.60722297430038452</v>
       </c>
       <c r="D65" s="2">
         <v>-0.096363365650177002</v>
       </c>
       <c r="E65" s="2">
-        <v>-0.43050423264503479</v>
+        <v>-0.42194825410842896</v>
       </c>
     </row>
     <row r="66">
@@ -1151,13 +1151,13 @@
         <v>-0.5292697548866272</v>
       </c>
       <c r="C66" s="2">
-        <v>-0.83615344762802124</v>
+        <v>-0.83571326732635498</v>
       </c>
       <c r="D66" s="2">
         <v>-0.1127610057592392</v>
       </c>
       <c r="E66" s="2">
-        <v>-0.45665323734283447</v>
+        <v>-0.44816118478775024</v>
       </c>
     </row>
     <row r="67">
@@ -1168,13 +1168,13 @@
         <v>0.7954375147819519</v>
       </c>
       <c r="C67" s="2">
-        <v>0.58548253774642944</v>
+        <v>0.59731549024581909</v>
       </c>
       <c r="D67" s="2">
         <v>-0.065585754811763763</v>
       </c>
       <c r="E67" s="2">
-        <v>-0.42106780409812927</v>
+        <v>-0.41337090730667114</v>
       </c>
     </row>
     <row r="68">
@@ -1185,13 +1185,13 @@
         <v>-0.47075435519218445</v>
       </c>
       <c r="C68" s="2">
-        <v>-0.80438238382339478</v>
+        <v>-0.7835390567779541</v>
       </c>
       <c r="D68" s="2">
         <v>-0.068046808242797852</v>
       </c>
       <c r="E68" s="2">
-        <v>-0.44981804490089417</v>
+        <v>-0.43941488862037659</v>
       </c>
     </row>
     <row r="69">
@@ -1202,13 +1202,13 @@
         <v>0.25346586108207703</v>
       </c>
       <c r="C69" s="2">
-        <v>-0.090113550424575806</v>
+        <v>-0.087198689579963684</v>
       </c>
       <c r="D69" s="2">
         <v>-0.078930631279945374</v>
       </c>
       <c r="E69" s="2">
-        <v>-0.46969485282897949</v>
+        <v>-0.45761212706565857</v>
       </c>
     </row>
     <row r="70">
@@ -1219,13 +1219,13 @@
         <v>0.24430331587791443</v>
       </c>
       <c r="C70" s="2">
-        <v>-0.19645890593528748</v>
+        <v>-0.18241408467292786</v>
       </c>
       <c r="D70" s="2">
         <v>-0.10793200135231018</v>
       </c>
       <c r="E70" s="2">
-        <v>-0.47897642850875854</v>
+        <v>-0.46727350354194641</v>
       </c>
     </row>
     <row r="71">
@@ -1236,13 +1236,13 @@
         <v>0.047511395066976547</v>
       </c>
       <c r="C71" s="2">
-        <v>-0.43422847986221313</v>
+        <v>-0.42667841911315918</v>
       </c>
       <c r="D71" s="2">
         <v>-0.15277969837188721</v>
       </c>
       <c r="E71" s="2">
-        <v>-0.49816536903381348</v>
+        <v>-0.48682126402854919</v>
       </c>
     </row>
     <row r="72">
@@ -1253,13 +1253,13 @@
         <v>-0.21580861508846283</v>
       </c>
       <c r="C72" s="2">
-        <v>-0.72107559442520142</v>
+        <v>-0.69804185628890991</v>
       </c>
       <c r="D72" s="2">
         <v>-0.21412444114685059</v>
       </c>
       <c r="E72" s="2">
-        <v>-0.57134461402893066</v>
+        <v>-0.56145340204238892</v>
       </c>
     </row>
     <row r="73">
@@ -1270,13 +1270,13 @@
         <v>-0.58863604068756104</v>
       </c>
       <c r="C73" s="2">
-        <v>-1.1167327165603638</v>
+        <v>-1.0950163602828979</v>
       </c>
       <c r="D73" s="2">
         <v>-0.20146757364273071</v>
       </c>
       <c r="E73" s="2">
-        <v>-0.53838640451431274</v>
+        <v>-0.53025311231613159</v>
       </c>
     </row>
     <row r="74">
@@ -1287,13 +1287,13 @@
         <v>-0.50763732194900513</v>
       </c>
       <c r="C74" s="2">
-        <v>-0.69712537527084351</v>
+        <v>-0.69417518377304077</v>
       </c>
       <c r="D74" s="2">
         <v>-0.24717943370342255</v>
       </c>
       <c r="E74" s="2">
-        <v>-0.57371270656585693</v>
+        <v>-0.5645102858543396</v>
       </c>
     </row>
     <row r="75">
@@ -1304,13 +1304,13 @@
         <v>-0.93289899826049805</v>
       </c>
       <c r="C75" s="2">
-        <v>-1.0088537931442261</v>
+        <v>-1.0116432905197144</v>
       </c>
       <c r="D75" s="2">
         <v>-0.31911718845367432</v>
       </c>
       <c r="E75" s="2">
-        <v>-0.62345558404922485</v>
+        <v>-0.6152271032333374</v>
       </c>
     </row>
     <row r="76">
@@ -1321,13 +1321,13 @@
         <v>0.24333480000495911</v>
       </c>
       <c r="C76" s="2">
-        <v>-0.07313062995672226</v>
+        <v>-0.074373885989189148</v>
       </c>
       <c r="D76" s="2">
         <v>-0.34663748741149902</v>
       </c>
       <c r="E76" s="2">
-        <v>-0.61919796466827393</v>
+        <v>-0.61114460229873657</v>
       </c>
     </row>
     <row r="77">
@@ -1338,13 +1338,13 @@
         <v>-0.35684254765510559</v>
       </c>
       <c r="C77" s="2">
-        <v>-0.50775885581970215</v>
+        <v>-0.50273609161376953</v>
       </c>
       <c r="D77" s="2">
         <v>-0.31957903504371643</v>
       </c>
       <c r="E77" s="2">
-        <v>-0.5639948844909668</v>
+        <v>-0.55854594707489014</v>
       </c>
     </row>
     <row r="78">
@@ -1355,13 +1355,13 @@
         <v>-0.15794084966182709</v>
       </c>
       <c r="C78" s="2">
-        <v>-0.4080500602722168</v>
+        <v>-0.39551353454589844</v>
       </c>
       <c r="D78" s="2">
         <v>-0.22663472592830658</v>
       </c>
       <c r="E78" s="2">
-        <v>-0.44186952710151672</v>
+        <v>-0.43737971782684326</v>
       </c>
     </row>
     <row r="79">
@@ -1372,13 +1372,13 @@
         <v>-0.40313661098480225</v>
       </c>
       <c r="C79" s="2">
-        <v>-0.64414465427398682</v>
+        <v>-0.63886517286300659</v>
       </c>
       <c r="D79" s="2">
         <v>-0.18005566298961639</v>
       </c>
       <c r="E79" s="2">
-        <v>-0.39551743865013123</v>
+        <v>-0.38992959260940552</v>
       </c>
     </row>
     <row r="80">
@@ -1389,13 +1389,13 @@
         <v>-0.20017130672931671</v>
       </c>
       <c r="C80" s="2">
-        <v>-0.39590990543365479</v>
+        <v>-0.38993605971336365</v>
       </c>
       <c r="D80" s="2">
         <v>-0.02626936137676239</v>
       </c>
       <c r="E80" s="2">
-        <v>-0.27408850193023682</v>
+        <v>-0.26796320080757141</v>
       </c>
     </row>
     <row r="81">
@@ -1406,13 +1406,13 @@
         <v>0.027717467397451401</v>
       </c>
       <c r="C81" s="2">
-        <v>-0.224248006939888</v>
+        <v>-0.22465415298938751</v>
       </c>
       <c r="D81" s="2">
         <v>-0.034426335245370865</v>
       </c>
       <c r="E81" s="2">
-        <v>-0.26072028279304504</v>
+        <v>-0.2529568076133728</v>
       </c>
     </row>
     <row r="82">
@@ -1423,13 +1423,13 @@
         <v>0.2478628009557724</v>
       </c>
       <c r="C82" s="2">
-        <v>-0.017604542896151543</v>
+        <v>-0.0045200162567198277</v>
       </c>
       <c r="D82" s="2">
         <v>0.03372843936085701</v>
       </c>
       <c r="E82" s="2">
-        <v>-0.21704863011837006</v>
+        <v>-0.20838896930217743</v>
       </c>
     </row>
     <row r="83">
@@ -1440,13 +1440,13 @@
         <v>-0.088425688445568085</v>
       </c>
       <c r="C83" s="2">
-        <v>-0.2799564003944397</v>
+        <v>-0.26712408661842346</v>
       </c>
       <c r="D83" s="2">
         <v>0.017333682626485825</v>
       </c>
       <c r="E83" s="2">
-        <v>-0.22952137887477875</v>
+        <v>-0.22210144996643066</v>
       </c>
     </row>
     <row r="84">
@@ -1457,13 +1457,13 @@
         <v>0.4511776864528656</v>
       </c>
       <c r="C84" s="2">
-        <v>0.084006480872631073</v>
+        <v>0.086054109036922455</v>
       </c>
       <c r="D84" s="2">
         <v>0.0051900632679462433</v>
       </c>
       <c r="E84" s="2">
-        <v>-0.23525558412075043</v>
+        <v>-0.22784751653671265</v>
       </c>
     </row>
     <row r="85">
@@ -1474,13 +1474,13 @@
         <v>0.16992203891277313</v>
       </c>
       <c r="C85" s="2">
-        <v>0.047183524817228317</v>
+        <v>0.060683857649564743</v>
       </c>
       <c r="D85" s="2">
         <v>0.030686743557453156</v>
       </c>
       <c r="E85" s="2">
-        <v>-0.19155406951904297</v>
+        <v>-0.18503355979919434</v>
       </c>
     </row>
     <row r="86">
@@ -1491,13 +1491,13 @@
         <v>0.25655040144920349</v>
       </c>
       <c r="C86" s="2">
-        <v>-0.114714115858078</v>
+        <v>-0.10162560641765594</v>
       </c>
       <c r="D86" s="2">
         <v>-0.00040994916344061494</v>
       </c>
       <c r="E86" s="2">
-        <v>-0.21345280110836029</v>
+        <v>-0.20632727444171906</v>
       </c>
     </row>
     <row r="87">
@@ -1508,13 +1508,13 @@
         <v>-0.30549365282058716</v>
       </c>
       <c r="C87" s="2">
-        <v>-0.52030473947525024</v>
+        <v>-0.51892590522766113</v>
       </c>
       <c r="D87" s="2">
         <v>-0.039005279541015625</v>
       </c>
       <c r="E87" s="2">
-        <v>-0.23432376980781555</v>
+        <v>-0.22894631326198578</v>
       </c>
     </row>
     <row r="88">
@@ -1525,13 +1525,13 @@
         <v>-0.51242917776107788</v>
       </c>
       <c r="C88" s="2">
-        <v>-0.69575250148773193</v>
+        <v>-0.69057983160018921</v>
       </c>
       <c r="D88" s="2">
         <v>-0.094004616141319275</v>
       </c>
       <c r="E88" s="2">
-        <v>-0.28699550032615662</v>
+        <v>-0.28275755047798157</v>
       </c>
     </row>
     <row r="89">
@@ -1542,13 +1542,13 @@
         <v>0.029298819601535797</v>
       </c>
       <c r="C89" s="2">
-        <v>-0.0025962803047150373</v>
+        <v>-0.0046104611828923225</v>
       </c>
       <c r="D89" s="2">
         <v>-0.15146702527999878</v>
       </c>
       <c r="E89" s="2">
-        <v>-0.32457232475280762</v>
+        <v>-0.31999659538269043</v>
       </c>
     </row>
     <row r="90">
@@ -1559,13 +1559,13 @@
         <v>-0.25215277075767517</v>
       </c>
       <c r="C90" s="2">
-        <v>-0.4213365912437439</v>
+        <v>-0.41629758477210999</v>
       </c>
       <c r="D90" s="2">
         <v>-0.18715491890907288</v>
       </c>
       <c r="E90" s="2">
-        <v>-0.38004526495933533</v>
+        <v>-0.37643611431121826</v>
       </c>
     </row>
     <row r="91">
@@ -1576,13 +1576,13 @@
         <v>-0.099495157599449158</v>
       </c>
       <c r="C91" s="2">
-        <v>-0.20544330775737762</v>
+        <v>-0.20809134840965271</v>
       </c>
       <c r="D91" s="2">
         <v>-0.22937063872814178</v>
       </c>
       <c r="E91" s="2">
-        <v>-0.37420555949211121</v>
+        <v>-0.37183663249015808</v>
       </c>
     </row>
     <row r="92">
@@ -1593,13 +1593,13 @@
         <v>-0.58341974020004272</v>
       </c>
       <c r="C92" s="2">
-        <v>-0.7540019154548645</v>
+        <v>-0.75142520666122437</v>
       </c>
       <c r="D92" s="2">
         <v>-0.24346867203712463</v>
       </c>
       <c r="E92" s="2">
-        <v>-0.4000873863697052</v>
+        <v>-0.39657452702522278</v>
       </c>
     </row>
     <row r="93">
@@ -1610,13 +1610,13 @@
         <v>-0.06598401814699173</v>
       </c>
       <c r="C93" s="2">
-        <v>-0.25418496131896973</v>
+        <v>-0.24909715354442596</v>
       </c>
       <c r="D93" s="2">
         <v>-0.21950669586658478</v>
       </c>
       <c r="E93" s="2">
-        <v>-0.37271407246589661</v>
+        <v>-0.37029087543487549</v>
       </c>
     </row>
     <row r="94">
@@ -1627,13 +1627,13 @@
         <v>-0.15126897394657135</v>
       </c>
       <c r="C94" s="2">
-        <v>-0.45207309722900391</v>
+        <v>-0.44727203249931335</v>
       </c>
       <c r="D94" s="2">
         <v>-0.23843617737293243</v>
       </c>
       <c r="E94" s="2">
-        <v>-0.41809466481208801</v>
+        <v>-0.41510903835296631</v>
       </c>
     </row>
     <row r="95">
@@ -1644,13 +1644,13 @@
         <v>-0.1233910396695137</v>
       </c>
       <c r="C95" s="2">
-        <v>-0.062156625092029572</v>
+        <v>-0.060230083763599396</v>
       </c>
       <c r="D95" s="2">
         <v>-0.12063248455524445</v>
       </c>
       <c r="E95" s="2">
-        <v>-0.31846067309379578</v>
+        <v>-0.31544509530067444</v>
       </c>
     </row>
     <row r="96">
@@ -1661,13 +1661,13 @@
         <v>-0.43237602710723877</v>
       </c>
       <c r="C96" s="2">
-        <v>-0.75324124097824097</v>
+        <v>-0.74156713485717773</v>
       </c>
       <c r="D96" s="2">
         <v>-0.091354772448539734</v>
       </c>
       <c r="E96" s="2">
-        <v>-0.31734803318977356</v>
+        <v>-0.31288343667984009</v>
       </c>
     </row>
     <row r="97">
@@ -1678,13 +1678,13 @@
         <v>-0.2967713475227356</v>
       </c>
       <c r="C97" s="2">
-        <v>-0.44939252734184265</v>
+        <v>-0.45402687788009644</v>
       </c>
       <c r="D97" s="2">
         <v>-0.079557500779628754</v>
       </c>
       <c r="E97" s="2">
-        <v>-0.30792030692100525</v>
+        <v>-0.30387324094772339</v>
       </c>
     </row>
     <row r="98">
@@ -1695,13 +1695,13 @@
         <v>-0.14106658101081848</v>
       </c>
       <c r="C98" s="2">
-        <v>-0.41102182865142822</v>
+        <v>-0.40797388553619385</v>
       </c>
       <c r="D98" s="2">
         <v>-0.0394136942923069</v>
       </c>
       <c r="E98" s="2">
-        <v>-0.2882331907749176</v>
+        <v>-0.28384974598884583</v>
       </c>
     </row>
     <row r="99">
@@ -1712,13 +1712,13 @@
         <v>0.80808055400848389</v>
       </c>
       <c r="C99" s="2">
-        <v>0.47536942362785339</v>
+        <v>0.48067778348922729</v>
       </c>
       <c r="D99" s="2">
         <v>-0.06220351904630661</v>
       </c>
       <c r="E99" s="2">
-        <v>-0.30071619153022766</v>
+        <v>-0.2970556914806366</v>
       </c>
     </row>
     <row r="100">
@@ -1729,13 +1729,13 @@
         <v>0.16400422155857086</v>
       </c>
       <c r="C100" s="2">
-        <v>-0.19542939960956573</v>
+        <v>-0.18503636121749878</v>
       </c>
       <c r="D100" s="2">
         <v>-0.074212342500686646</v>
       </c>
       <c r="E100" s="2">
-        <v>-0.35366103053092957</v>
+        <v>-0.35069409012794495</v>
       </c>
     </row>
     <row r="101">
@@ -1746,13 +1746,13 @@
         <v>-0.47724428772926331</v>
       </c>
       <c r="C101" s="2">
-        <v>-0.66915237903594971</v>
+        <v>-0.67033344507217407</v>
       </c>
       <c r="D101" s="2">
         <v>-0.10567409545183182</v>
       </c>
       <c r="E101" s="2">
-        <v>-0.37862983345985413</v>
+        <v>-0.37599152326583862</v>
       </c>
     </row>
     <row r="102">
@@ -1763,13 +1763,13 @@
         <v>0.29531022906303406</v>
       </c>
       <c r="C102" s="2">
-        <v>-0.077001169323921204</v>
+        <v>-0.068885646760463715</v>
       </c>
       <c r="D102" s="2">
         <v>-0.055531982332468033</v>
       </c>
       <c r="E102" s="2">
-        <v>-0.33176529407501221</v>
+        <v>-0.32742080092430115</v>
       </c>
     </row>
     <row r="103">
@@ -1780,13 +1780,13 @@
         <v>-0.35637739300727844</v>
       </c>
       <c r="C103" s="2">
-        <v>-0.56442004442214966</v>
+        <v>-0.56612557172775269</v>
       </c>
       <c r="D103" s="2">
         <v>0.016286512836813927</v>
       </c>
       <c r="E103" s="2">
-        <v>-0.25880521535873413</v>
+        <v>-0.25303283333778381</v>
       </c>
     </row>
     <row r="104">
@@ -1797,13 +1797,13 @@
         <v>-0.23147046566009521</v>
       </c>
       <c r="C104" s="2">
-        <v>-0.53866016864776611</v>
+        <v>-0.54297572374343872</v>
       </c>
       <c r="D104" s="2">
         <v>-0.16860204935073853</v>
       </c>
       <c r="E104" s="2">
-        <v>-0.43719446659088135</v>
+        <v>-0.42996835708618164</v>
       </c>
     </row>
     <row r="105">
@@ -1814,13 +1814,13 @@
         <v>-0.71553176641464233</v>
       </c>
       <c r="C105" s="2">
-        <v>-0.97796052694320679</v>
+        <v>-0.96924400329589844</v>
       </c>
       <c r="D105" s="2">
         <v>-0.15435120463371277</v>
       </c>
       <c r="E105" s="2">
-        <v>-0.40607616305351257</v>
+        <v>-0.39898517727851868</v>
       </c>
     </row>
     <row r="106">
@@ -1831,13 +1831,13 @@
         <v>0.15450765192508698</v>
       </c>
       <c r="C106" s="2">
-        <v>-0.027611576020717621</v>
+        <v>-0.016890361905097961</v>
       </c>
       <c r="D106" s="2">
         <v>-0.063373111188411713</v>
       </c>
       <c r="E106" s="2">
-        <v>-0.30539503693580627</v>
+        <v>-0.29843971133232117</v>
       </c>
     </row>
     <row r="107">
@@ -1848,13 +1848,13 @@
         <v>0.50529986619949341</v>
       </c>
       <c r="C107" s="2">
-        <v>0.24561889469623566</v>
+        <v>0.26151776313781738</v>
       </c>
       <c r="D107" s="2">
         <v>-0.089116953313350677</v>
       </c>
       <c r="E107" s="2">
-        <v>-0.29146614670753479</v>
+        <v>-0.28577446937561035</v>
       </c>
     </row>
     <row r="108">
@@ -1865,13 +1865,13 @@
         <v>-0.85591655969619751</v>
       </c>
       <c r="C108" s="2">
-        <v>-1.1301338672637939</v>
+        <v>-1.1117417812347412</v>
       </c>
       <c r="D108" s="2">
         <v>-0.08382522314786911</v>
       </c>
       <c r="E108" s="2">
-        <v>-0.27632617950439453</v>
+        <v>-0.27097094058990479</v>
       </c>
     </row>
     <row r="109">
@@ -1882,13 +1882,13 @@
         <v>0.29226183891296387</v>
       </c>
       <c r="C109" s="2">
-        <v>0.084635399281978607</v>
+        <v>0.09381219744682312</v>
       </c>
       <c r="D109" s="2">
         <v>-0.19660459458827972</v>
       </c>
       <c r="E109" s="2">
-        <v>-0.36580654978752136</v>
+        <v>-0.36014315485954285</v>
       </c>
     </row>
     <row r="110">
@@ -1899,13 +1899,13 @@
         <v>0.34155860543251038</v>
       </c>
       <c r="C110" s="2">
-        <v>0.23697769641876221</v>
+        <v>0.2345757931470871</v>
       </c>
       <c r="D110" s="2">
         <v>-0.22061219811439514</v>
       </c>
       <c r="E110" s="2">
-        <v>-0.38279062509536743</v>
+        <v>-0.37700369954109192</v>
       </c>
     </row>
     <row r="111">
@@ -1916,13 +1916,13 @@
         <v>0.06361563503742218</v>
       </c>
       <c r="C111" s="2">
-        <v>0.048358969390392303</v>
+        <v>0.04510156437754631</v>
       </c>
       <c r="D111" s="2">
         <v>-0.32563570141792297</v>
       </c>
       <c r="E111" s="2">
-        <v>-0.4687170684337616</v>
+        <v>-0.46444177627563477</v>
       </c>
     </row>
     <row r="112">
@@ -1933,13 +1933,13 @@
         <v>-0.30875179171562195</v>
       </c>
       <c r="C112" s="2">
-        <v>-0.42816036939620972</v>
+        <v>-0.43289387226104736</v>
       </c>
       <c r="D112" s="2">
         <v>-0.48997443914413452</v>
       </c>
       <c r="E112" s="2">
-        <v>-0.61922025680541992</v>
+        <v>-0.61665970087051392</v>
       </c>
     </row>
     <row r="113">
@@ -1950,13 +1950,13 @@
         <v>-1.2464848756790161</v>
       </c>
       <c r="C113" s="2">
-        <v>-1.3439836502075195</v>
+        <v>-1.3455257415771484</v>
       </c>
       <c r="D113" s="2">
         <v>-0.45804888010025024</v>
       </c>
       <c r="E113" s="2">
-        <v>-0.57867574691772461</v>
+        <v>-0.57722955942153931</v>
       </c>
     </row>
     <row r="114">
@@ -1967,13 +1967,13 @@
         <v>-0.93160015344619751</v>
       </c>
       <c r="C114" s="2">
-        <v>-1.1308170557022095</v>
+        <v>-1.1209887266159058</v>
       </c>
       <c r="D114" s="2">
         <v>-0.58391422033309937</v>
       </c>
       <c r="E114" s="2">
-        <v>-0.69239151477813721</v>
+        <v>-0.69179987907409668</v>
       </c>
     </row>
     <row r="115">
@@ -1984,13 +1984,13 @@
         <v>-0.79070389270782471</v>
       </c>
       <c r="C115" s="2">
-        <v>-0.80094969272613525</v>
+        <v>-0.80383306741714478</v>
       </c>
       <c r="D115" s="2">
         <v>-0.60402911901473999</v>
       </c>
       <c r="E115" s="2">
-        <v>-0.69588828086853027</v>
+        <v>-0.69503617286682129</v>
       </c>
     </row>
     <row r="116">
@@ -2001,13 +2001,13 @@
         <v>-0.97374874353408813</v>
       </c>
       <c r="C116" s="2">
-        <v>-1.1089098453521729</v>
+        <v>-1.1084436178207397</v>
       </c>
       <c r="D116" s="2">
         <v>-0.63690668344497681</v>
       </c>
       <c r="E116" s="2">
-        <v>-0.7337462306022644</v>
+        <v>-0.7315259575843811</v>
       </c>
     </row>
     <row r="117">
@@ -2018,13 +2018,13 @@
         <v>-0.56858664751052856</v>
       </c>
       <c r="C117" s="2">
-        <v>-0.76523292064666748</v>
+        <v>-0.75687062740325928</v>
       </c>
       <c r="D117" s="2">
         <v>-0.61852693557739258</v>
       </c>
       <c r="E117" s="2">
-        <v>-0.71638971567153931</v>
+        <v>-0.71338182687759399</v>
       </c>
     </row>
     <row r="118">
@@ -2035,13 +2035,13 @@
         <v>-0.8405260443687439</v>
       </c>
       <c r="C118" s="2">
-        <v>-0.93880671262741089</v>
+        <v>-0.93732070922851562</v>
       </c>
       <c r="D118" s="2">
         <v>-0.5726659893989563</v>
       </c>
       <c r="E118" s="2">
-        <v>-0.66688072681427002</v>
+        <v>-0.66364079713821411</v>
       </c>
     </row>
     <row r="119">
@@ -2052,13 +2052,13 @@
         <v>0.16052468121051788</v>
       </c>
       <c r="C119" s="2">
-        <v>0.2055065929889679</v>
+        <v>0.20544902980327606</v>
       </c>
       <c r="D119" s="2">
         <v>-0.54333215951919556</v>
       </c>
       <c r="E119" s="2">
-        <v>-0.63886642456054688</v>
+        <v>-0.63565218448638916</v>
       </c>
     </row>
     <row r="120">
@@ -2069,13 +2069,13 @@
         <v>-0.2322828620672226</v>
       </c>
       <c r="C120" s="2">
-        <v>-0.29236260056495667</v>
+        <v>-0.28330636024475098</v>
       </c>
       <c r="D120" s="2">
         <v>-0.53246229887008667</v>
       </c>
       <c r="E120" s="2">
-        <v>-0.64264547824859619</v>
+        <v>-0.63899391889572144</v>
       </c>
     </row>
     <row r="121">
@@ -2086,13 +2086,13 @@
         <v>-0.14333407580852509</v>
       </c>
       <c r="C121" s="2">
-        <v>-0.2719515860080719</v>
+        <v>-0.26959657669067383</v>
       </c>
       <c r="D121" s="2">
         <v>-0.53456318378448486</v>
       </c>
       <c r="E121" s="2">
-        <v>-0.6565203070640564</v>
+        <v>-0.65217882394790649</v>
       </c>
     </row>
     <row r="122">
@@ -2103,13 +2103,13 @@
         <v>-0.83373624086380005</v>
       </c>
       <c r="C122" s="2">
-        <v>-0.89840292930603027</v>
+        <v>-0.89785677194595337</v>
       </c>
       <c r="D122" s="2">
         <v>-0.50244688987731934</v>
       </c>
       <c r="E122" s="2">
-        <v>-0.64065128564834595</v>
+        <v>-0.63634270429611206</v>
       </c>
     </row>
     <row r="123">
@@ -2120,13 +2120,13 @@
         <v>-0.66759538650512695</v>
       </c>
       <c r="C123" s="2">
-        <v>-0.8786882758140564</v>
+        <v>-0.86909091472625732</v>
       </c>
       <c r="D123" s="2">
         <v>-0.43224349617958069</v>
       </c>
       <c r="E123" s="2">
-        <v>-0.59371459484100342</v>
+        <v>-0.58867937326431274</v>
       </c>
     </row>
     <row r="124">
@@ -2137,13 +2137,13 @@
         <v>-0.6928754448890686</v>
       </c>
       <c r="C124" s="2">
-        <v>-0.83496105670928955</v>
+        <v>-0.8339085578918457</v>
       </c>
       <c r="D124" s="2">
         <v>-0.46384522318840027</v>
       </c>
       <c r="E124" s="2">
-        <v>-0.65432173013687134</v>
+        <v>-0.64899575710296631</v>
       </c>
     </row>
     <row r="125">
@@ -2154,13 +2154,13 @@
         <v>-0.99265658855438232</v>
       </c>
       <c r="C125" s="2">
-        <v>-1.2337833642959595</v>
+        <v>-1.2271081209182739</v>
       </c>
       <c r="D125" s="2">
         <v>-0.42486768960952759</v>
       </c>
       <c r="E125" s="2">
-        <v>-0.6493486762046814</v>
+        <v>-0.64307940006256104</v>
       </c>
     </row>
     <row r="126">
@@ -2171,13 +2171,13 @@
         <v>-0.2795403003692627</v>
       </c>
       <c r="C126" s="2">
-        <v>-0.62241172790527344</v>
+        <v>-0.61434519290924072</v>
       </c>
       <c r="D126" s="2">
         <v>-0.41055825352668762</v>
       </c>
       <c r="E126" s="2">
-        <v>-0.65857589244842529</v>
+        <v>-0.65134590864181519</v>
       </c>
     </row>
     <row r="127">
@@ -2188,13 +2188,13 @@
         <v>-0.20869520306587219</v>
       </c>
       <c r="C127" s="2">
-        <v>-0.51637649536132812</v>
+        <v>-0.508350670337677</v>
       </c>
       <c r="D127" s="2">
         <v>-0.37319645285606384</v>
       </c>
       <c r="E127" s="2">
-        <v>-0.6545373797416687</v>
+        <v>-0.64635562896728516</v>
       </c>
     </row>
     <row r="128">
@@ -2205,13 +2205,13 @@
         <v>-0.1238909438252449</v>
       </c>
       <c r="C128" s="2">
-        <v>-0.33995729684829712</v>
+        <v>-0.33739840984344482</v>
       </c>
       <c r="D128" s="2">
         <v>-0.38565275073051453</v>
       </c>
       <c r="E128" s="2">
-        <v>-0.66187423467636108</v>
+        <v>-0.65479415655136108</v>
       </c>
     </row>
     <row r="129">
@@ -2222,13 +2222,13 @@
         <v>0.11851492524147034</v>
       </c>
       <c r="C129" s="2">
-        <v>-0.24760521948337555</v>
+        <v>-0.23005962371826172</v>
       </c>
       <c r="D129" s="2">
         <v>-0.3713735044002533</v>
       </c>
       <c r="E129" s="2">
-        <v>-0.64820742607116699</v>
+        <v>-0.64064192771911621</v>
       </c>
     </row>
     <row r="130">
@@ -2239,13 +2239,13 @@
         <v>-0.014549159444868565</v>
       </c>
       <c r="C130" s="2">
-        <v>-0.35499680042266846</v>
+        <v>-0.34399503469467163</v>
       </c>
       <c r="D130" s="2">
         <v>-0.3302956223487854</v>
       </c>
       <c r="E130" s="2">
-        <v>-0.62483847141265869</v>
+        <v>-0.61604434251785278</v>
       </c>
     </row>
     <row r="131">
@@ -2256,13 +2256,13 @@
         <v>-0.49747994542121887</v>
       </c>
       <c r="C131" s="2">
-        <v>-0.86205631494522095</v>
+        <v>-0.852944016456604</v>
       </c>
       <c r="D131" s="2">
         <v>-0.2482590526342392</v>
       </c>
       <c r="E131" s="2">
-        <v>-0.53256702423095703</v>
+        <v>-0.52268463373184204</v>
       </c>
     </row>
     <row r="132">
@@ -2273,13 +2273,13 @@
         <v>-0.77970212697982788</v>
       </c>
       <c r="C132" s="2">
-        <v>-0.94472008943557739</v>
+        <v>-0.94503796100616455</v>
       </c>
       <c r="D132" s="2">
         <v>-0.28857755661010742</v>
       </c>
       <c r="E132" s="2">
-        <v>-0.55870336294174194</v>
+        <v>-0.54910957813262939</v>
       </c>
     </row>
     <row r="133">
@@ -2290,13 +2290,13 @@
         <v>-0.5643622875213623</v>
       </c>
       <c r="C133" s="2">
-        <v>-0.71195971965789795</v>
+        <v>-0.70653825998306274</v>
       </c>
       <c r="D133" s="2">
         <v>-0.31260773539543152</v>
       </c>
       <c r="E133" s="2">
-        <v>-0.58255696296691895</v>
+        <v>-0.57162517309188843</v>
       </c>
     </row>
     <row r="134">
@@ -2307,13 +2307,13 @@
         <v>-0.62295544147491455</v>
       </c>
       <c r="C134" s="2">
-        <v>-1.0234626531600952</v>
+        <v>-1.0057300329208374</v>
       </c>
       <c r="D134" s="2">
         <v>-0.35904130339622498</v>
       </c>
       <c r="E134" s="2">
-        <v>-0.59823280572891235</v>
+        <v>-0.59068280458450317</v>
       </c>
     </row>
     <row r="135">
@@ -2324,13 +2324,13 @@
         <v>0.45878866314888</v>
       </c>
       <c r="C135" s="2">
-        <v>0.20803150534629822</v>
+        <v>0.22589223086833954</v>
       </c>
       <c r="D135" s="2">
         <v>-0.41105476021766663</v>
       </c>
       <c r="E135" s="2">
-        <v>-0.62000107765197754</v>
+        <v>-0.61390697956085205</v>
       </c>
     </row>
     <row r="136">
@@ -2341,13 +2341,13 @@
         <v>-0.57156169414520264</v>
       </c>
       <c r="C136" s="2">
-        <v>-0.75160354375839233</v>
+        <v>-0.74617528915405273</v>
       </c>
       <c r="D136" s="2">
         <v>-0.38155457377433777</v>
       </c>
       <c r="E136" s="2">
-        <v>-0.56558668613433838</v>
+        <v>-0.56017082929611206</v>
       </c>
     </row>
     <row r="137">
@@ -2358,13 +2358,13 @@
         <v>-0.34016242623329163</v>
       </c>
       <c r="C137" s="2">
-        <v>-0.55463987588882446</v>
+        <v>-0.54003870487213135</v>
       </c>
       <c r="D137" s="2">
-        <v>-0.33178612589836121</v>
+        <v>-0.37788259983062744</v>
       </c>
       <c r="E137" s="2">
-        <v>-0.51819503307342529</v>
+        <v>-0.54821896553039551</v>
       </c>
     </row>
     <row r="138">
@@ -2375,13 +2375,13 @@
         <v>-0.29938742518424988</v>
       </c>
       <c r="C138" s="2">
-        <v>-0.3886878490447998</v>
+        <v>-0.4015783965587616</v>
       </c>
       <c r="D138" s="2">
-        <v>-0.2985609769821167</v>
+        <v>-0.35476464033126831</v>
       </c>
       <c r="E138" s="2">
-        <v>-0.4905143678188324</v>
+        <v>-0.54200482368469238</v>
       </c>
     </row>
     <row r="139">
@@ -2392,13 +2392,13 @@
         <v>-0.48267009854316711</v>
       </c>
       <c r="C139" s="2">
-        <v>-0.55091136693954468</v>
+        <v>-0.55301225185394287</v>
       </c>
       <c r="D139" s="2">
-        <v>-0.2444952130317688</v>
+        <v>-0.29230538010597229</v>
       </c>
       <c r="E139" s="2">
-        <v>-0.40168964862823486</v>
+        <v>-0.46170878410339355</v>
       </c>
     </row>
     <row r="140">
@@ -2409,95 +2409,239 @@
         <v>-0.23197831213474274</v>
       </c>
       <c r="C140" s="2">
-        <v>-0.37232685089111328</v>
+        <v>-0.36931887269020081</v>
       </c>
       <c r="D140" s="2">
-        <v>-0.38515198230743408</v>
+        <v>-0.36356052756309509</v>
       </c>
       <c r="E140" s="2">
-        <v>-0.52363389730453491</v>
+        <v>-0.53368520736694336</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1">
         <v>45505</v>
       </c>
-      <c r="B141" s="2"/>
-      <c r="C141" s="2"/>
-      <c r="D141" s="2"/>
-      <c r="E141" s="2"/>
+      <c r="B141" s="2">
+        <v>-0.74665433168411255</v>
+      </c>
+      <c r="C141" s="2">
+        <v>-0.83747124671936035</v>
+      </c>
+      <c r="D141" s="2">
+        <v>-0.3734951913356781</v>
+      </c>
+      <c r="E141" s="2">
+        <v>-0.54413563013076782</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1">
         <v>45536</v>
       </c>
-      <c r="B142" s="2"/>
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
+      <c r="B142" s="2">
+        <v>-0.35630065202713013</v>
+      </c>
+      <c r="C142" s="2">
+        <v>-0.65061110258102417</v>
+      </c>
+      <c r="D142" s="2">
+        <v>-0.41878041625022888</v>
+      </c>
+      <c r="E142" s="2">
+        <v>-0.58618336915969849</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1">
         <v>45566</v>
       </c>
-      <c r="B143" s="2"/>
-      <c r="C143" s="2"/>
-      <c r="D143" s="2"/>
-      <c r="E143" s="2"/>
+      <c r="B143" s="2">
+        <v>-0.060822233557701111</v>
+      </c>
+      <c r="C143" s="2">
+        <v>-0.28306534886360168</v>
+      </c>
+      <c r="D143" s="2">
+        <v>-0.46153551340103149</v>
+      </c>
+      <c r="E143" s="2">
+        <v>-0.6357424259185791</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1">
         <v>45597</v>
       </c>
-      <c r="B144" s="2"/>
-      <c r="C144" s="2"/>
-      <c r="D144" s="2"/>
-      <c r="E144" s="2"/>
+      <c r="B144" s="2">
+        <v>-0.18250758945941925</v>
+      </c>
+      <c r="C144" s="2">
+        <v>-0.42189592123031616</v>
+      </c>
+      <c r="D144" s="2">
+        <v>-0.44945114850997925</v>
+      </c>
+      <c r="E144" s="2">
+        <v>-0.63770896196365356</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1">
         <v>45627</v>
       </c>
-      <c r="B145" s="2"/>
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
-      <c r="E145" s="2"/>
+      <c r="B145" s="2">
+        <v>-0.66097366809844971</v>
+      </c>
+      <c r="C145" s="2">
+        <v>-0.84022873640060425</v>
+      </c>
+      <c r="D145" s="2">
+        <v>-0.46189159154891968</v>
+      </c>
+      <c r="E145" s="2">
+        <v>-0.65854531526565552</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1">
         <v>45658</v>
       </c>
-      <c r="B146" s="2"/>
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
-      <c r="E146" s="2"/>
+      <c r="B146" s="2">
+        <v>-0.74772936105728149</v>
+      </c>
+      <c r="C146" s="2">
+        <v>-0.9184684157371521</v>
+      </c>
+      <c r="D146" s="2">
+        <v>-0.42629626393318176</v>
+      </c>
+      <c r="E146" s="2">
+        <v>-0.63617956638336182</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1">
         <v>45689</v>
       </c>
-      <c r="B147" s="2"/>
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
-      <c r="E147" s="2"/>
+      <c r="B147" s="2">
+        <v>-0.68418329954147339</v>
+      </c>
+      <c r="C147" s="2">
+        <v>-0.8476099967956543</v>
+      </c>
+      <c r="D147" s="2">
+        <v>-0.43629562854766846</v>
+      </c>
+      <c r="E147" s="2">
+        <v>-0.63411796092987061</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1">
         <v>45717</v>
       </c>
-      <c r="B148" s="2"/>
-      <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
-      <c r="E148" s="2"/>
+      <c r="B148" s="2">
+        <v>-0.37391075491905212</v>
+      </c>
+      <c r="C148" s="2">
+        <v>-0.57071083784103394</v>
+      </c>
+      <c r="D148" s="2">
+        <v>-0.49887454509735107</v>
+      </c>
+      <c r="E148" s="2">
+        <v>-0.6926267147064209</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1">
         <v>45748</v>
       </c>
-      <c r="B149" s="2"/>
-      <c r="C149" s="2"/>
-      <c r="D149" s="2"/>
-      <c r="E149" s="2"/>
+      <c r="B149" s="2">
+        <v>-0.3439425528049469</v>
+      </c>
+      <c r="C149" s="2">
+        <v>-0.55684632062911987</v>
+      </c>
+      <c r="D149" s="2">
+        <v>-0.56214791536331177</v>
+      </c>
+      <c r="E149" s="2">
+        <v>-0.7467728853225708</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="2"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="2"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="2"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
     </row>
   </sheetData>
 </worksheet>
